--- a/SPEC MyBook Pro M7T.xlsx
+++ b/SPEC MyBook Pro M7T.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MyBook PRO\Downloads\Spec\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MyBook PRO\Desktop\axioo_b2g\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39A7F481-0BC5-4968-8E2F-B4CA9A0A1E56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F2BD18-1BF1-459E-8E90-49A2BA718A84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,12 +53,159 @@
     <t>Intel® Processor i7-1355U(10 Core 12 Threads, Base TDP: 15W)</t>
   </si>
   <si>
+    <t>Code Name</t>
+  </si>
+  <si>
+    <t>Raptor Lake</t>
+  </si>
+  <si>
+    <t>Graphics Controller</t>
+  </si>
+  <si>
+    <t>Intel® Iris Xe Graphics eligible</t>
+  </si>
+  <si>
+    <t>LCD</t>
+  </si>
+  <si>
+    <t>14" inch IPS (16:10)</t>
+  </si>
+  <si>
+    <t>Display  / Resolution</t>
+  </si>
+  <si>
+    <t>WUXGA 1920x1200</t>
+  </si>
+  <si>
+    <t>Memory RAM</t>
+  </si>
+  <si>
+    <t>2x SODIMM DDR4 Up to 32GB per Channel,Frequency Up to 3200MHz</t>
+  </si>
+  <si>
+    <t>Storage</t>
+  </si>
+  <si>
+    <t>1x M.2 SATA/ NVMe PCIe Gen. 4x4 | 1x M.2 NVME PCIe Support Gen. 4x4</t>
+  </si>
+  <si>
+    <t>Camera Front</t>
+  </si>
+  <si>
+    <t>2Mpx</t>
+  </si>
+  <si>
+    <t>Sound System</t>
+  </si>
+  <si>
+    <t>Realtek® Audio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built-in Microphone </t>
+  </si>
+  <si>
+    <t>I/O Ports</t>
+  </si>
+  <si>
+    <t>3x USB 3.2 Gen1 Type A ports</t>
+  </si>
+  <si>
+    <t>2x USB 3.0 Type C port (Full Function: Data, Power, Video)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1x 3.5mm 2-in-1 Audio Combo Jack </t>
+  </si>
+  <si>
+    <t>1x HDMI 2.0 output port</t>
+  </si>
+  <si>
+    <t>1x VGA port</t>
+  </si>
+  <si>
+    <t>1x RJ45 port</t>
+  </si>
+  <si>
+    <t>1x DC-in jack port</t>
+  </si>
+  <si>
+    <t>1x Micro SD Card Port</t>
+  </si>
+  <si>
+    <t>Power Management</t>
+  </si>
+  <si>
+    <t>AC Adapter 19V/3.42A, 64.98W</t>
+  </si>
+  <si>
+    <t>Embedded 3 cells Li-polymer battery pack, 11.5V,57Wh, 4936mAh</t>
+  </si>
+  <si>
+    <t>Connection</t>
+  </si>
+  <si>
+    <t>Wi-Fi Intel 9560 ac/b/g/n</t>
+  </si>
+  <si>
+    <t>Gigabit LAN</t>
+  </si>
+  <si>
+    <t>Speaker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2x Speakers  </t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>TPM 2.0</t>
+  </si>
+  <si>
+    <t>Kensington Lock</t>
+  </si>
+  <si>
+    <t>Bios</t>
+  </si>
+  <si>
+    <t>AMI</t>
+  </si>
+  <si>
+    <t>O.S</t>
+  </si>
+  <si>
+    <t>Windows® 11 (64-bit)</t>
+  </si>
+  <si>
+    <t>Dimension</t>
+  </si>
+  <si>
+    <t>315.6(W) x 231.2(D) x 18.9(H)mm</t>
+  </si>
+  <si>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>1.81Kg</t>
+  </si>
+  <si>
+    <t>Other Design</t>
+  </si>
+  <si>
+    <t>Cover A &amp; Cover D Metal</t>
+  </si>
+  <si>
+    <t>Touchscreen Panel</t>
+  </si>
+  <si>
+    <t>Finger print</t>
+  </si>
+  <si>
     <r>
       <t>Performance Cores:</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -73,7 +220,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -83,151 +230,13 @@
     </r>
   </si>
   <si>
-    <t>Code Name</t>
-  </si>
-  <si>
-    <t>Raptor Lake</t>
-  </si>
-  <si>
-    <t>Graphics Controller</t>
-  </si>
-  <si>
-    <t>Intel® Iris Xe Graphics eligible</t>
-  </si>
-  <si>
-    <t>LCD</t>
-  </si>
-  <si>
-    <t>14" inch IPS (16:10)</t>
-  </si>
-  <si>
-    <t>Display  / Resolution</t>
-  </si>
-  <si>
-    <t>WUXGA 1920x1200</t>
-  </si>
-  <si>
-    <t>Memory RAM</t>
-  </si>
-  <si>
-    <t>2x SODIMM DDR4 Up to 32GB per Channel,Frequency Up to 3200MHz</t>
-  </si>
-  <si>
-    <t>Storage</t>
-  </si>
-  <si>
-    <t>1x M.2 SATA/ NVMe PCIe Gen. 4x4 | 1x M.2 NVME PCIe Support Gen. 4x4</t>
-  </si>
-  <si>
-    <t>Camera Front</t>
-  </si>
-  <si>
-    <t>2Mpx</t>
-  </si>
-  <si>
-    <t>Sound System</t>
-  </si>
-  <si>
-    <t>Realtek® Audio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Built-in Microphone </t>
-  </si>
-  <si>
-    <t>I/O Ports</t>
-  </si>
-  <si>
-    <t>3x USB 3.2 Gen1 Type A ports</t>
-  </si>
-  <si>
-    <t>2x USB 3.0 Type C port (Full Function: Data, Power, Video)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1x 3.5mm 2-in-1 Audio Combo Jack </t>
-  </si>
-  <si>
-    <t>1x HDMI 2.0 output port</t>
-  </si>
-  <si>
-    <t>1x VGA port</t>
-  </si>
-  <si>
-    <t>1x RJ45 port</t>
-  </si>
-  <si>
-    <t>1x DC-in jack port</t>
-  </si>
-  <si>
-    <t>1x Micro SD Card Port</t>
-  </si>
-  <si>
-    <t>Power Management</t>
-  </si>
-  <si>
-    <t>AC Adapter 19V/3.42A, 64.98W</t>
-  </si>
-  <si>
-    <t>Embedded 3 cells Li-polymer battery pack, 11.5V,57Wh, 4936mAh</t>
-  </si>
-  <si>
-    <t>Connection</t>
-  </si>
-  <si>
-    <t>Wi-Fi Intel 9560 ac/b/g/n</t>
-  </si>
-  <si>
-    <t>Gigabit LAN</t>
-  </si>
-  <si>
-    <t>Speaker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2x Speakers  </t>
-  </si>
-  <si>
-    <t>Security</t>
-  </si>
-  <si>
-    <t>TPM 2.0</t>
-  </si>
-  <si>
-    <t>Kensington Lock</t>
-  </si>
-  <si>
-    <t>Bios</t>
-  </si>
-  <si>
-    <t>AMI</t>
-  </si>
-  <si>
-    <t>O.S</t>
-  </si>
-  <si>
-    <t>Windows® 11 (64-bit)</t>
-  </si>
-  <si>
-    <t>Dimension</t>
-  </si>
-  <si>
-    <t>315.6(W) x 231.2(D) x 18.9(H)mm</t>
-  </si>
-  <si>
-    <t>weight</t>
-  </si>
-  <si>
-    <t>1.81Kg</t>
-  </si>
-  <si>
-    <t>Other Design</t>
-  </si>
-  <si>
     <r>
       <t>180</t>
     </r>
     <r>
       <rPr>
         <b/>
-        <sz val="11"/>
+        <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -237,7 +246,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="11"/>
+        <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -245,15 +254,6 @@
       </rPr>
       <t xml:space="preserve"> Hinge Rotate</t>
     </r>
-  </si>
-  <si>
-    <t>Cover A &amp; Cover D Metal</t>
-  </si>
-  <si>
-    <t>Touchscreen Panel</t>
-  </si>
-  <si>
-    <t>Finger print</t>
   </si>
 </sst>
 </file>
@@ -270,56 +270,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -330,30 +283,77 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color indexed="8"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -439,103 +439,103 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -845,315 +845,316 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D47"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15" style="34" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="51.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="20"/>
-      <c r="B3" s="18"/>
+      <c r="A3" s="4"/>
+      <c r="B3" s="5"/>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="31" t="s">
+      <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="7" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="32"/>
-      <c r="B5" s="28" t="s">
+      <c r="A5" s="8"/>
+      <c r="B5" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="10"/>
+      <c r="B6" s="11" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="7" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="33"/>
-      <c r="B6" s="29" t="s">
+      <c r="B7" s="7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="24" t="s">
+    <row r="8" spans="1:4" ht="13.2">
+      <c r="A8" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B8" s="12" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="15">
-      <c r="A8" s="24" t="s">
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B9" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="21" t="s">
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B10" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="19" t="s">
+    <row r="11" spans="1:4">
+      <c r="A11" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B11" s="7" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="24" t="s">
+      <c r="D11" s="16"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B12" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="23"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="25" t="s">
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B13" s="18" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="24" t="s">
+      <c r="D13" s="19"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B14" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="17"/>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="34" t="s">
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="20"/>
+      <c r="B15" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="10" t="s">
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="20" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="34"/>
-      <c r="B15" s="12" t="s">
+      <c r="B16" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="34" t="s">
+    <row r="17" spans="1:2">
+      <c r="A17" s="20"/>
+      <c r="B17" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="10" t="s">
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="20"/>
+      <c r="B18" s="18" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="34"/>
-      <c r="B17" s="26" t="s">
+    <row r="19" spans="1:2">
+      <c r="A19" s="20"/>
+      <c r="B19" s="22" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="34"/>
-      <c r="B18" s="13" t="s">
+    <row r="20" spans="1:2">
+      <c r="A20" s="20"/>
+      <c r="B20" s="22" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="34"/>
-      <c r="B19" s="14" t="s">
+    <row r="21" spans="1:2">
+      <c r="A21" s="20"/>
+      <c r="B21" s="22" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="34"/>
-      <c r="B20" s="14" t="s">
+    <row r="22" spans="1:2">
+      <c r="A22" s="20"/>
+      <c r="B22" s="7" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="34"/>
-      <c r="B21" s="14" t="s">
+    <row r="23" spans="1:2">
+      <c r="A23" s="20"/>
+      <c r="B23" s="18" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="34"/>
-      <c r="B22" s="10" t="s">
+    <row r="24" spans="1:2">
+      <c r="A24" s="20" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="34"/>
-      <c r="B23" s="13" t="s">
+      <c r="B24" s="7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="34" t="s">
+    <row r="25" spans="1:2">
+      <c r="A25" s="20"/>
+      <c r="B25" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="B24" s="10" t="s">
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="20" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="34"/>
-      <c r="B25" s="13" t="s">
+      <c r="B26" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="34" t="s">
+    <row r="27" spans="1:2">
+      <c r="A27" s="20"/>
+      <c r="B27" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="B26" s="9" t="s">
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="7" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="34"/>
-      <c r="B27" s="13" t="s">
+      <c r="B28" s="7" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="24" t="s">
+    <row r="29" spans="1:2">
+      <c r="A29" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B29" s="7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
-      <c r="A29" s="34" t="s">
+    <row r="30" spans="1:2">
+      <c r="A30" s="20"/>
+      <c r="B30" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="10" t="s">
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="7" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="34"/>
-      <c r="B30" s="10" t="s">
+      <c r="B31" s="7" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="24" t="s">
+    <row r="32" spans="1:2">
+      <c r="A32" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B32" s="23" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
-      <c r="A32" s="24" t="s">
+    <row r="33" spans="1:4" ht="13.2">
+      <c r="A33" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B32" s="15" t="s">
+      <c r="B33" s="18" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" ht="15">
-      <c r="A33" s="24" t="s">
+      <c r="C33" s="24"/>
+      <c r="D33" s="24"/>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B33" s="13" t="s">
+      <c r="B34" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="C33" s="16"/>
-      <c r="D33" s="16"/>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="24" t="s">
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B34" s="13" t="s">
+      <c r="B35" s="25" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="8"/>
+      <c r="B36" s="25" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="31" t="s">
+    <row r="37" spans="1:4">
+      <c r="A37" s="8"/>
+      <c r="B37" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="B35" s="27" t="s">
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="10"/>
+      <c r="B38" s="26" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="32"/>
-      <c r="B36" s="27" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="32"/>
-      <c r="B37" s="27" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="33"/>
-      <c r="B38" s="30" t="s">
-        <v>56</v>
-      </c>
-    </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="3"/>
-      <c r="B39" s="17"/>
+      <c r="A39" s="27"/>
+      <c r="B39" s="19"/>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="3"/>
-      <c r="B40" s="17"/>
+      <c r="A40" s="27"/>
+      <c r="B40" s="19"/>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="2"/>
-      <c r="B41" s="4"/>
+      <c r="A41" s="28"/>
+      <c r="B41" s="29"/>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
+      <c r="A43" s="28"/>
+      <c r="B43" s="30"/>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
+      <c r="A44" s="28"/>
+      <c r="B44" s="30"/>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="5"/>
-      <c r="B45" s="6"/>
+      <c r="A45" s="31"/>
+      <c r="B45" s="32"/>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="7"/>
+      <c r="A46" s="33"/>
     </row>
     <row r="47" spans="1:4">
-      <c r="B47" s="4"/>
+      <c r="B47" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -1171,6 +1172,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="189b1353-a086-487c-981c-f6344e352306" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f82bd302-08e5-41cf-ac7e-929bc680f927">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007F1C94A586F6A64AA956C7CA2AB05C9B" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7b39dff72ebd7b03cdb9d3443bb53f9a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f82bd302-08e5-41cf-ac7e-929bc680f927" xmlns:ns3="189b1353-a086-487c-981c-f6344e352306" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6783e78daab35a5ff41903a679763a9d" ns2:_="" ns3:_="">
     <xsd:import namespace="f82bd302-08e5-41cf-ac7e-929bc680f927"/>
@@ -1405,27 +1426,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D5B5D2E-7482-4704-9D9B-A1FF914A381E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="189b1353-a086-487c-981c-f6344e352306"/>
+    <ds:schemaRef ds:uri="f82bd302-08e5-41cf-ac7e-929bc680f927"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="189b1353-a086-487c-981c-f6344e352306" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f82bd302-08e5-41cf-ac7e-929bc680f927">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89F5F491-8E5F-4BB3-BC05-D109E566801C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4543B697-20C2-426C-9B8C-2306D94C423A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1442,23 +1462,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89F5F491-8E5F-4BB3-BC05-D109E566801C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D5B5D2E-7482-4704-9D9B-A1FF914A381E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="189b1353-a086-487c-981c-f6344e352306"/>
-    <ds:schemaRef ds:uri="f82bd302-08e5-41cf-ac7e-929bc680f927"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>